--- a/assets/ESR Formations-France.xlsx
+++ b/assets/ESR Formations-France.xlsx
@@ -5,20 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR_NewRecruit/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9EFA18F7C2E81EA4/Documents/NewRecruit/ESR/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{5B5579AA-790E-4F9F-96D2-3CC922622812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A40298A-4141-4D0C-81FD-739E2DE810FF}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="8_{5B5579AA-790E-4F9F-96D2-3CC922622812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65B8DF88-E23F-4AB1-A86D-53F948B9E1DD}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="0" windowWidth="26610" windowHeight="14700" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="2190" yWindow="1605" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
     <sheet name="ExpandedFormations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$2)</definedName>
-    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$2)</definedName>
+    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$3)</definedName>
+    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$3)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="69">
   <si>
     <t>Formation</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>FR Brigade de Cavalerie de la Garde Impériale</t>
+  </si>
+  <si>
+    <t>FR Mixed</t>
+  </si>
+  <si>
+    <t>Mixed</t>
   </si>
 </sst>
 </file>
@@ -434,10 +440,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -458,10 +464,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -816,34 +818,34 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12"/>
+      <c r="C2" s="13"/>
       <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="9"/>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>20</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
       <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="3">
         <v>12</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="F3" s="13"/>
       <c r="I3" s="8" t="s">
         <v>47</v>
       </c>
@@ -852,16 +854,16 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="3">
         <v>1</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="13"/>
       <c r="I4" s="8" t="s">
         <v>48</v>
       </c>
@@ -897,17 +899,17 @@
       <c r="A6" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="9"/>
-      <c r="F6" s="12"/>
+      <c r="F6" s="13"/>
       <c r="I6" s="8" t="s">
         <v>50</v>
       </c>
@@ -916,16 +918,16 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
       <c r="D7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="3">
         <v>4</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="13"/>
       <c r="I7" s="8" t="s">
         <v>51</v>
       </c>
@@ -934,16 +936,16 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="3">
         <v>2</v>
       </c>
-      <c r="F8" s="12"/>
+      <c r="F8" s="13"/>
       <c r="I8" s="8" t="s">
         <v>52</v>
       </c>
@@ -952,14 +954,14 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
       <c r="D9" s="2"/>
       <c r="E9" s="3">
         <v>1</v>
       </c>
-      <c r="F9" s="12"/>
+      <c r="F9" s="13"/>
       <c r="I9" s="8" t="s">
         <v>53</v>
       </c>
@@ -968,13 +970,13 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -983,7 +985,7 @@
       <c r="E10" s="5">
         <v>9</v>
       </c>
-      <c r="F10" s="13"/>
+      <c r="F10" s="12"/>
       <c r="I10" s="8" t="s">
         <v>54</v>
       </c>
@@ -992,16 +994,16 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
       <c r="D11" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="5">
         <v>1</v>
       </c>
-      <c r="F11" s="13"/>
+      <c r="F11" s="12"/>
       <c r="I11" s="8" t="s">
         <v>55</v>
       </c>
@@ -1010,13 +1012,13 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -1025,7 +1027,7 @@
       <c r="E12" s="3">
         <v>9</v>
       </c>
-      <c r="F12" s="12"/>
+      <c r="F12" s="13"/>
       <c r="I12" s="8" t="s">
         <v>56</v>
       </c>
@@ -1034,16 +1036,16 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
       <c r="D13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="3">
         <v>1</v>
       </c>
-      <c r="F13" s="12"/>
+      <c r="F13" s="13"/>
       <c r="I13" s="8" t="s">
         <v>57</v>
       </c>
@@ -1052,13 +1054,13 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -1067,7 +1069,7 @@
       <c r="E14" s="5">
         <v>1</v>
       </c>
-      <c r="F14" s="13"/>
+      <c r="F14" s="12"/>
       <c r="I14" s="8" t="s">
         <v>58</v>
       </c>
@@ -1076,16 +1078,16 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
       <c r="D15" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E15" s="5">
         <v>1</v>
       </c>
-      <c r="F15" s="13"/>
+      <c r="F15" s="12"/>
       <c r="I15" s="8" t="s">
         <v>29</v>
       </c>
@@ -1094,16 +1096,16 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
       <c r="D16" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="5">
         <v>1</v>
       </c>
-      <c r="F16" s="13"/>
+      <c r="F16" s="12"/>
       <c r="I16" s="8" t="s">
         <v>30</v>
       </c>
@@ -1112,16 +1114,16 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="4" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="5">
         <v>2</v>
       </c>
-      <c r="F17" s="13"/>
+      <c r="F17" s="12"/>
       <c r="I17" s="8" t="s">
         <v>31</v>
       </c>
@@ -1279,6 +1281,10 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="F14:F17"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="F2:F4"/>
@@ -1295,10 +1301,6 @@
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B14:B17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1306,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A52F401-E5BC-41DA-8596-65382229DEB1}">
-  <dimension ref="A1:AG9"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -1416,47 +1418,128 @@
         <v>FR 6-pdr Artillerie à Cheval</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:C9">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
+    <row r="2" spans="1:33" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG2" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" t="str" cm="1">
+        <f t="array" ref="A3:C10">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
         <v>FR Division d’Infanterie</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B3" t="str">
         <v>Infantry</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C3" t="str">
         <v/>
       </c>
-      <c r="V2" t="s">
-        <v>28</v>
-      </c>
-      <c r="W2" t="s">
-        <v>28</v>
-      </c>
-      <c r="X2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <v>FR Brigade de Cavalerie Légère</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Cavalry</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Rapid Deployment</v>
-      </c>
-      <c r="AC3" t="s">
+      <c r="V3" t="s">
+        <v>28</v>
+      </c>
+      <c r="W3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF3" t="s">
         <v>28</v>
       </c>
       <c r="AG3" t="s">
@@ -1465,7 +1548,7 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <v>FR Division de Cavalerie Légère</v>
+        <v>FR Brigade de Cavalerie Légère</v>
       </c>
       <c r="B4" t="str">
         <v>Cavalry</v>
@@ -1473,13 +1556,7 @@
       <c r="C4" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="AB4" t="s">
-        <v>28</v>
-      </c>
       <c r="AC4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD4" t="s">
         <v>28</v>
       </c>
       <c r="AG4" t="s">
@@ -1488,7 +1565,7 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <v>FR Division de Cavalerie/Dragons</v>
+        <v>FR Division de Cavalerie Légère</v>
       </c>
       <c r="B5" t="str">
         <v>Cavalry</v>
@@ -1496,7 +1573,13 @@
       <c r="C5" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD5" t="s">
         <v>28</v>
       </c>
       <c r="AG5" t="s">
@@ -1505,7 +1588,7 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <v>FR Division de Grosse Cavalerie</v>
+        <v>FR Division de Cavalerie/Dragons</v>
       </c>
       <c r="B6" t="str">
         <v>Cavalry</v>
@@ -1513,13 +1596,7 @@
       <c r="C6" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="Y6" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AB6" t="s">
+      <c r="AA6" t="s">
         <v>28</v>
       </c>
       <c r="AG6" t="s">
@@ -1528,18 +1605,21 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <v>FR Corps Réserve/Parc d’Artillerie</v>
+        <v>FR Division de Grosse Cavalerie</v>
       </c>
       <c r="B7" t="str">
-        <v>Artillery</v>
+        <v>Cavalry</v>
       </c>
       <c r="C7" t="str">
-        <v>Reinforcements</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF7" t="s">
+        <v>Rapid Deployment</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB7" t="s">
         <v>28</v>
       </c>
       <c r="AG7" t="s">
@@ -1548,80 +1628,100 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <v>FR Division d’Infanterie de la Garde Impériale</v>
+        <v>FR Corps Réserve/Parc d’Artillerie</v>
       </c>
       <c r="B8" t="str">
-        <v>Infantry</v>
+        <v>Artillery</v>
       </c>
       <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" t="s">
-        <v>28</v>
-      </c>
-      <c r="R8" t="s">
-        <v>28</v>
-      </c>
-      <c r="S8" t="s">
-        <v>28</v>
-      </c>
-      <c r="T8" t="s">
-        <v>28</v>
-      </c>
-      <c r="U8" t="s">
+        <v>Reinforcements</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
+        <v>FR Division d’Infanterie de la Garde Impériale</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Infantry</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" t="s">
+        <v>28</v>
+      </c>
+      <c r="R9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S9" t="s">
+        <v>28</v>
+      </c>
+      <c r="T9" t="s">
+        <v>28</v>
+      </c>
+      <c r="U9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
         <v>FR Brigade de Cavalerie de la Garde Impériale</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B10" t="str">
         <v>Cavalry</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C10" t="str">
         <v>Rapid Deployment</v>
       </c>
-      <c r="K9" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" t="s">
-        <v>28</v>
-      </c>
-      <c r="N9" t="s">
-        <v>28</v>
-      </c>
-      <c r="O9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P9" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="K10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>28</v>
+      </c>
+      <c r="S10" t="s">
         <v>28</v>
       </c>
     </row>
